--- a/assets_management/tests/data/asset_asset.xlsx
+++ b/assets_management/tests/data/asset_asset.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -58,13 +58,13 @@
     <t xml:space="preserve">z0bug.asset_category_1</t>
   </si>
   <si>
+    <t xml:space="preserve">100.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">####-##-##</t>
+  </si>
+  <si>
     <t xml:space="preserve">base.main_company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">####-##-##</t>
   </si>
   <si>
     <t xml:space="preserve">z0bug.asset_2</t>
@@ -359,17 +359,15 @@
       <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -385,14 +383,12 @@
       <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -405,14 +401,12 @@
       <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="2"/>
+      <c r="F4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -425,14 +419,12 @@
       <c r="D5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/assets_management/tests/data/asset_asset.xlsx
+++ b/assets_management/tests/data/asset_asset.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -88,10 +88,16 @@
     <t xml:space="preserve">Test asset #3</t>
   </si>
   <si>
+    <t xml:space="preserve">z0bug.asset_category_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">z0bug.asset_4</t>
   </si>
   <si>
     <t xml:space="preserve">Test asset #4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.asset_category_4</t>
   </si>
 </sst>
 </file>
@@ -399,7 +405,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="1" t="s">
@@ -411,13 +417,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="1" t="s">

--- a/assets_management/tests/data/asset_asset.xlsx
+++ b/assets_management/tests/data/asset_asset.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -98,6 +98,15 @@
   </si>
   <si>
     <t xml:space="preserve">z0bug.asset_category_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.asset_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test asset #0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0</t>
   </si>
 </sst>
 </file>
@@ -313,7 +322,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.4"/>
@@ -433,6 +442,27 @@
         <v>13</v>
       </c>
     </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
